--- a/LubanTools/DesignerConfigs/Datas/Bridge/bridge_config.xlsx
+++ b/LubanTools/DesignerConfigs/Datas/Bridge/bridge_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>0;1;1|0;-1;0</t>
+  </si>
+  <si>
+    <t>桥头</t>
   </si>
 </sst>
 </file>
@@ -1148,8 +1151,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.375" style="2" customWidth="1"/>
@@ -1343,6 +1346,28 @@
         <v>27</v>
       </c>
     </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7">
+        <v>300005</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f>"bridge_"&amp;B9</f>
+        <v>bridge_300005</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
